--- a/Main/Resources/Templates/AIP.xlsx
+++ b/Main/Resources/Templates/AIP.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yabut\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yabut\source\repos\myps_backend\Main\Resources\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C24A696B-AD73-4849-88F1-019341B9F78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7614907-462A-42E0-B01D-2D5693367A42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BD463D73-1456-481D-947B-5DAD403531E8}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BD463D73-1456-481D-947B-5DAD403531E8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -222,10 +222,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="16" x14ac:knownFonts="1">
     <font>
@@ -381,7 +380,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
@@ -390,25 +389,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
@@ -419,85 +406,90 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="19" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="4"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="19" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" indent="4"/>
     </xf>
   </cellXfs>
   <cellStyles count="18">
@@ -830,7 +822,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B3E30D1-162B-4B44-89DA-C2BBC8366B66}">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.140625" customWidth="1"/>
@@ -845,321 +837,339 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
     </row>
     <row r="2" spans="1:10" ht="26.25" x14ac:dyDescent="0.4">
-      <c r="A2" s="22">
+      <c r="A2" s="15">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
     </row>
     <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-    </row>
-    <row r="4" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="22">
+      <c r="C3" s="27"/>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="27"/>
+    </row>
+    <row r="4" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A4" s="15"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="15">
         <v>2</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="3" t="s">
+      <c r="B5" s="9"/>
+      <c r="C5" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3"/>
-      <c r="E4" s="30" t="s">
+      <c r="D5" s="32"/>
+      <c r="E5" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="31" t="s">
+      <c r="F5" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="30" t="s">
+      <c r="G5" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="30" t="s">
+      <c r="H5" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="30" t="s">
+      <c r="I5" s="33" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="30" t="s">
+      <c r="J5" s="33" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="22">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="15">
         <v>3</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-    </row>
-    <row r="6" spans="1:10" ht="21.75" x14ac:dyDescent="0.4">
-      <c r="A6" s="22">
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+    </row>
+    <row r="7" spans="1:10" ht="21.75" x14ac:dyDescent="0.4">
+      <c r="A7" s="15">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B7" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="14" t="s">
+      <c r="C7" s="30"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I7" s="8">
         <v>100000000</v>
       </c>
-      <c r="J6" s="14"/>
-    </row>
-    <row r="7" spans="1:10" ht="21.75" x14ac:dyDescent="0.4">
-      <c r="A7" s="22">
+      <c r="J7" s="10"/>
+    </row>
+    <row r="8" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="15">
         <v>5</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="40" t="s">
+      <c r="B8" s="5"/>
+      <c r="C8" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="14" t="s">
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I8" s="8">
         <v>100000000</v>
       </c>
-      <c r="J7" s="14"/>
-    </row>
-    <row r="8" spans="1:10" ht="17.25" x14ac:dyDescent="0.4">
-      <c r="A8" s="22">
+      <c r="J8" s="10"/>
+    </row>
+    <row r="9" spans="1:10" ht="17.25" x14ac:dyDescent="0.4">
+      <c r="A9" s="15">
         <v>6</v>
       </c>
-      <c r="B8" s="10"/>
-      <c r="C8" s="15" t="s">
+      <c r="B9" s="6"/>
+      <c r="C9" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="14" t="s">
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I9" s="8">
         <v>100000000</v>
       </c>
-      <c r="J8" s="14"/>
-    </row>
-    <row r="9" spans="1:10" ht="21.75" x14ac:dyDescent="0.4">
-      <c r="A9" s="22" t="s">
+      <c r="J9" s="10"/>
+    </row>
+    <row r="10" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="9"/>
-      <c r="C9" s="40" t="s">
+      <c r="B10" s="5"/>
+      <c r="C10" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="14" t="s">
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="36"/>
+      <c r="H10" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I10" s="8">
         <v>100000000</v>
       </c>
-      <c r="J9" s="14"/>
-    </row>
-    <row r="10" spans="1:10" ht="17.25" x14ac:dyDescent="0.4">
-      <c r="A10" s="41">
+      <c r="J10" s="10"/>
+    </row>
+    <row r="11" spans="1:10" ht="17.25" x14ac:dyDescent="0.4">
+      <c r="A11" s="25">
         <v>7</v>
       </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="16" t="s">
+      <c r="B11" s="6"/>
+      <c r="C11" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="14" t="s">
+      <c r="D11" s="37"/>
+      <c r="E11" s="37"/>
+      <c r="F11" s="37"/>
+      <c r="G11" s="37"/>
+      <c r="H11" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I11" s="8">
         <v>100000000</v>
       </c>
-      <c r="J10" s="9"/>
-    </row>
-    <row r="11" spans="1:10" ht="17.25" x14ac:dyDescent="0.4">
-      <c r="A11" s="41">
+      <c r="J11" s="5"/>
+    </row>
+    <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="25">
         <v>8</v>
       </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="17" t="s">
+      <c r="B12" s="6"/>
+      <c r="C12" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="12">
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="8">
         <v>100000000</v>
       </c>
-      <c r="J11" s="9"/>
-    </row>
-    <row r="12" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="41">
+      <c r="J12" s="5"/>
+    </row>
+    <row r="13" spans="1:10" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A13" s="25">
         <v>9</v>
       </c>
-      <c r="B12" s="32" t="s">
+      <c r="B13" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C13" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D13" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36" t="s">
+      <c r="E13" s="29"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="I12" s="29">
+      <c r="I13" s="18">
         <v>100000000</v>
       </c>
-      <c r="J12" s="34" t="s">
+      <c r="J13" s="21" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="41">
+    <row r="14" spans="1:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="25">
         <v>10</v>
       </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="4" t="s">
+      <c r="B14" s="7"/>
+      <c r="C14" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="28"/>
-    </row>
-    <row r="14" spans="1:10" ht="75" x14ac:dyDescent="0.25">
-      <c r="A14" s="41">
+      <c r="D14" s="28"/>
+      <c r="E14" s="28"/>
+      <c r="F14" s="28"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A15" s="25">
         <v>11</v>
       </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="38" t="s">
+      <c r="B15" s="6"/>
+      <c r="C15" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="D14" s="19"/>
-      <c r="E14" s="20" t="s">
+      <c r="D15" s="31"/>
+      <c r="E15" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="F15" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="19" t="s">
+      <c r="G15" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="19">
+      <c r="H15" s="12">
         <v>12.509</v>
       </c>
-      <c r="I14" s="21">
+      <c r="I15" s="14">
         <v>96500000</v>
       </c>
-      <c r="J14" s="20" t="s">
+      <c r="J15" s="13" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="22"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="19"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="21"/>
-      <c r="J15" s="20"/>
-    </row>
-    <row r="16" spans="1:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="22">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="15"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="24"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="13"/>
+    </row>
+    <row r="17" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="15">
         <v>12</v>
       </c>
-      <c r="B16" s="10"/>
-      <c r="C16" s="24" t="s">
+      <c r="B17" s="6"/>
+      <c r="C17" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D17" s="17">
         <v>0.5083333333333333</v>
       </c>
-      <c r="E16" s="23"/>
-      <c r="F16" s="26"/>
-      <c r="G16" s="23"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21" t="s">
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14" t="s">
         <v>32</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="12">
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="B7:G7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
